--- a/artfynd/A 28822-2023 artfynd.xlsx
+++ b/artfynd/A 28822-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28822-2023 artfynd.xlsx
+++ b/artfynd/A 28822-2023 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>112061969</v>
       </c>
       <c r="B4" t="n">
-        <v>90831</v>
+        <v>92272</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,21 +940,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>3100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372297</v>
+        <v>372298</v>
       </c>
       <c r="R4" t="n">
-        <v>6860805</v>
+        <v>6860806</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 28822-2023 artfynd.xlsx
+++ b/artfynd/A 28822-2023 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>112061969</v>
       </c>
       <c r="B4" t="n">
-        <v>92272</v>
+        <v>92289</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 28822-2023 artfynd.xlsx
+++ b/artfynd/A 28822-2023 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>112061969</v>
       </c>
       <c r="B4" t="n">
-        <v>92289</v>
+        <v>92294</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 28822-2023 artfynd.xlsx
+++ b/artfynd/A 28822-2023 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>112061969</v>
       </c>
       <c r="B4" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
